--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/post FET_HRM-2031-0392/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/post FET_HRM-2031-0392/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.7481</v>
+        <v>16.81611</v>
       </c>
       <c r="D2" t="n">
-        <v>16.68911</v>
+        <v>16.36832</v>
       </c>
       <c r="E2" t="n">
-        <v>16.81148</v>
+        <v>16.80277</v>
       </c>
       <c r="F2" t="n">
-        <v>43.42626</v>
+        <v>44.15524</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05047</v>
+        <v>0.05129</v>
       </c>
       <c r="H2" t="n">
-        <v>1.82937</v>
+        <v>1.82104</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.57572</v>
+        <v>16.60092</v>
       </c>
       <c r="D3" t="n">
-        <v>16.54527</v>
+        <v>16.52793</v>
       </c>
       <c r="E3" t="n">
-        <v>16.54943</v>
+        <v>16.53747</v>
       </c>
       <c r="F3" t="n">
-        <v>41.90117</v>
+        <v>42.72134</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05147</v>
+        <v>0.04961</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83612</v>
+        <v>1.85293</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.01885</v>
+        <v>17.25437</v>
       </c>
       <c r="D4" t="n">
-        <v>16.58716</v>
+        <v>16.76622</v>
       </c>
       <c r="E4" t="n">
-        <v>16.44178</v>
+        <v>16.91259</v>
       </c>
       <c r="F4" t="n">
-        <v>43.42219</v>
+        <v>43.25828</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05138</v>
+        <v>0.05025</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83619</v>
+        <v>1.84791</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.80474</v>
+        <v>16.81441</v>
       </c>
       <c r="D6" t="n">
-        <v>16.06602</v>
+        <v>16.15128</v>
       </c>
       <c r="E6" t="n">
-        <v>16.84002</v>
+        <v>16.61224</v>
       </c>
       <c r="F6" t="n">
-        <v>22.32981</v>
+        <v>22.12367</v>
       </c>
       <c r="G6" t="n">
-        <v>34.39591</v>
+        <v>34.51879</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.75484</v>
+        <v>16.85465</v>
       </c>
       <c r="D7" t="n">
-        <v>15.95919</v>
+        <v>16.24799</v>
       </c>
       <c r="E7" t="n">
-        <v>16.68012</v>
+        <v>16.49314</v>
       </c>
       <c r="F7" t="n">
-        <v>21.94674</v>
+        <v>22.14386</v>
       </c>
       <c r="G7" t="n">
-        <v>33.77338</v>
+        <v>34.73758</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.78168</v>
+        <v>16.88694</v>
       </c>
       <c r="D8" t="n">
-        <v>16.07906</v>
+        <v>16.01901</v>
       </c>
       <c r="E8" t="n">
-        <v>16.46411</v>
+        <v>16.34729</v>
       </c>
       <c r="F8" t="n">
-        <v>21.86883</v>
+        <v>22.14067</v>
       </c>
       <c r="G8" t="n">
-        <v>34.45381</v>
+        <v>33.93818</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.60982</v>
+        <v>0.60808</v>
       </c>
       <c r="D10" t="n">
-        <v>1.11825</v>
+        <v>1.116</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.61232</v>
+        <v>0.6011</v>
       </c>
       <c r="D11" t="n">
-        <v>1.12472</v>
+        <v>1.0919</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.62202</v>
+        <v>0.61085</v>
       </c>
       <c r="D12" t="n">
-        <v>1.12236</v>
+        <v>1.10991</v>
       </c>
     </row>
   </sheetData>
